--- a/informes_data/Segunda FEB/2025-26/playoffs/individual/NP_play_by_play_2513086_ELIMINATORIAS14FINAL_PROCESSED.xlsx
+++ b/informes_data/Segunda FEB/2025-26/playoffs/individual/NP_play_by_play_2513086_ELIMINATORIAS14FINAL_PROCESSED.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>P. GARCIA CARRERO</t>
+          <t>R. FABREGA URPINA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.187</v>
+        <v>4.4659</v>
       </c>
       <c r="E2" t="n">
-        <v>3.1402</v>
+        <v>2.5657</v>
       </c>
       <c r="F2" t="n">
-        <v>1.0467</v>
+        <v>1.9002</v>
       </c>
       <c r="G2" t="n">
-        <v>3.6108</v>
+        <v>5.1596</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5763</v>
+        <v>0.8101</v>
       </c>
       <c r="I2" t="n">
-        <v>3.0344</v>
+        <v>4.3496</v>
       </c>
       <c r="J2" t="n">
-        <v>2.7904</v>
+        <v>4.4295</v>
       </c>
       <c r="K2" t="n">
-        <v>0.8001</v>
+        <v>1.3611</v>
       </c>
       <c r="L2" t="n">
-        <v>1.9903</v>
+        <v>3.0684</v>
       </c>
       <c r="M2" t="n">
-        <v>0.8204</v>
+        <v>0.7302</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.2238</v>
+        <v>-0.551</v>
       </c>
       <c r="O2" t="n">
-        <v>1.0442</v>
+        <v>1.2812</v>
       </c>
       <c r="P2" t="n">
-        <v>1.6388</v>
+        <v>-0.2025</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-2.0245</v>
       </c>
       <c r="R2" t="n">
-        <v>1.6388</v>
+        <v>1.8221</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8264</v>
+        <v>-0.4913</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6981000000000001</v>
+        <v>-0.0902</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1283</v>
+        <v>-0.4011</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.889</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.3482</v>
+        <v>0.2509</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.5407</v>
+        <v>-0.2509</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R. FABREGA URPINA</t>
+          <t>K. NEWTON</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.0261</v>
+        <v>3.3391</v>
       </c>
       <c r="E3" t="n">
-        <v>1.7702</v>
+        <v>1.6592</v>
       </c>
       <c r="F3" t="n">
-        <v>2.2559</v>
+        <v>1.6799</v>
       </c>
       <c r="G3" t="n">
-        <v>5.135</v>
+        <v>3.099</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8028999999999999</v>
+        <v>0.5341</v>
       </c>
       <c r="I3" t="n">
-        <v>4.3321</v>
+        <v>2.5649</v>
       </c>
       <c r="J3" t="n">
-        <v>4.3375</v>
+        <v>2.4483</v>
       </c>
       <c r="K3" t="n">
-        <v>1.3054</v>
+        <v>0.0395</v>
       </c>
       <c r="L3" t="n">
-        <v>3.0322</v>
+        <v>2.4088</v>
       </c>
       <c r="M3" t="n">
-        <v>0.7975</v>
+        <v>0.6506999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.5024999999999999</v>
+        <v>0.4945</v>
       </c>
       <c r="O3" t="n">
-        <v>1.3</v>
+        <v>0.1561</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.2048</v>
+        <v>-0.2025</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.0485</v>
+        <v>-1.0123</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8436</v>
+        <v>0.8098</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.9041</v>
+        <v>0.4426</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7609</v>
+        <v>0.2232</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1432</v>
+        <v>0.2194</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.2421</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>K. NEWTON</t>
+          <t>P. GARCIA CARRERO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.7749</v>
+        <v>3.0146</v>
       </c>
       <c r="E4" t="n">
-        <v>1.9743</v>
+        <v>2.6931</v>
       </c>
       <c r="F4" t="n">
-        <v>1.8006</v>
+        <v>0.3215</v>
       </c>
       <c r="G4" t="n">
-        <v>3.0883</v>
+        <v>3.5691</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5406</v>
+        <v>0.5358000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>2.5477</v>
+        <v>3.0333</v>
       </c>
       <c r="J4" t="n">
-        <v>2.4245</v>
+        <v>2.8212</v>
       </c>
       <c r="K4" t="n">
-        <v>0.039</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>2.3854</v>
+        <v>2.0112</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6639</v>
+        <v>0.7479</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5016</v>
+        <v>-0.2742</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1623</v>
+        <v>1.022</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.2048</v>
+        <v>1.6196</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.0242</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8194</v>
+        <v>1.6196</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8914</v>
+        <v>-0.2698</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5741000000000001</v>
+        <v>0.2161</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3173</v>
+        <v>-0.4858</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-1.9043</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>-0.3442</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.5602</v>
       </c>
     </row>
     <row r="5">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.2582</v>
+        <v>2.5667</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.3046</v>
+        <v>-0.3719</v>
       </c>
       <c r="F5" t="n">
-        <v>3.5628</v>
+        <v>2.9386</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.4668</v>
+        <v>-0.4521</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.8561</v>
+        <v>-1.8392</v>
       </c>
       <c r="I5" t="n">
-        <v>1.3893</v>
+        <v>1.3871</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.9755</v>
+        <v>-0.8817</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.7159</v>
+        <v>-1.6443</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7403</v>
+        <v>0.7625999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5088</v>
+        <v>0.4296</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1402</v>
+        <v>-0.1949</v>
       </c>
       <c r="O5" t="n">
-        <v>0.649</v>
+        <v>0.6245000000000001</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2048</v>
+        <v>0.2025</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.0485</v>
+        <v>-2.0245</v>
       </c>
       <c r="R5" t="n">
-        <v>2.2533</v>
+        <v>2.227</v>
       </c>
       <c r="S5" t="n">
-        <v>1.0527</v>
+        <v>0.3428</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7065</v>
+        <v>0.4981</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3462</v>
+        <v>-0.1553</v>
       </c>
       <c r="V5" t="n">
-        <v>2.4674</v>
+        <v>2.4736</v>
       </c>
       <c r="W5" t="n">
-        <v>2.013</v>
+        <v>2.0362</v>
       </c>
       <c r="X5" t="n">
-        <v>0.4544</v>
+        <v>0.4374</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. SAEZ GIL</t>
+          <t>O. RUSSELL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.159</v>
+        <v>0.5511</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>-1.1967</v>
       </c>
       <c r="F6" t="n">
-        <v>0.159</v>
+        <v>1.7477</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1394</v>
+        <v>1.439</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>-1.422</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1394</v>
+        <v>2.8609</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1.1466</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>-1.2459</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.3925</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1394</v>
+        <v>0.2923</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>-0.1761</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1394</v>
+        <v>0.4684</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-2.4294</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-4.049</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.6196</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0196</v>
+        <v>-0.0315</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>0.0136</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0196</v>
+        <v>-0.0452</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.573</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.6921</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.119</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>I. ROSA POMPIDO</t>
+          <t>D. SAEZ GIL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1145</v>
+        <v>0.1864</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2495</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.364</v>
+        <v>0.1864</v>
       </c>
       <c r="G7" t="n">
-        <v>1.4764</v>
+        <v>0.1384</v>
       </c>
       <c r="H7" t="n">
-        <v>1.2685</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2079</v>
+        <v>0.1384</v>
       </c>
       <c r="J7" t="n">
-        <v>1.2967</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>1.4362</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.1395</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1797</v>
+        <v>0.1384</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1677</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3474</v>
+        <v>0.1384</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.0242</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.0485</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.0242</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1.0981</v>
+        <v>0.048</v>
       </c>
       <c r="T7" t="n">
-        <v>0.8207</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2774</v>
+        <v>0.048</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.6647</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.1806</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.8453</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>O. RUSSELL</t>
+          <t>I. ROSA POMPIDO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5789</v>
+        <v>-0.3316</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.1552</v>
+        <v>1.1467</v>
       </c>
       <c r="F8" t="n">
-        <v>1.5762</v>
+        <v>-1.4783</v>
       </c>
       <c r="G8" t="n">
-        <v>1.4503</v>
+        <v>1.5092</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.3968</v>
+        <v>1.2841</v>
       </c>
       <c r="I8" t="n">
-        <v>2.8472</v>
+        <v>0.2252</v>
       </c>
       <c r="J8" t="n">
-        <v>1.1035</v>
+        <v>1.3755</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.2569</v>
+        <v>1.4803</v>
       </c>
       <c r="L8" t="n">
-        <v>2.3604</v>
+        <v>-0.1048</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3468</v>
+        <v>0.1337</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1399</v>
+        <v>-0.1962</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4868</v>
+        <v>0.33</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.4582</v>
+        <v>-1.0123</v>
       </c>
       <c r="Q8" t="n">
-        <v>-4.097</v>
+        <v>-2.0245</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6388</v>
+        <v>1.0123</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.1177</v>
+        <v>0.8635</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8264</v>
+        <v>0.6054</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2913</v>
+        <v>0.258</v>
       </c>
       <c r="V8" t="n">
-        <v>1.5467</v>
+        <v>-1.6921</v>
       </c>
       <c r="W8" t="n">
-        <v>1.6647</v>
+        <v>1.1902</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1181</v>
+        <v>-2.8823</v>
       </c>
     </row>
     <row r="9">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.4749</v>
+        <v>-0.9581</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.2188</v>
+        <v>-2.9411</v>
       </c>
       <c r="F9" t="n">
-        <v>1.7439</v>
+        <v>1.983</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.8906</v>
+        <v>-1.8989</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.7288</v>
+        <v>-2.7279</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8381999999999999</v>
+        <v>0.8290999999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.6099</v>
+        <v>-2.5898</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.7285</v>
+        <v>-2.7091</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1185</v>
+        <v>0.1193</v>
       </c>
       <c r="M9" t="n">
-        <v>0.7194</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0003</v>
+        <v>-0.0188</v>
       </c>
       <c r="O9" t="n">
-        <v>0.7197</v>
+        <v>0.7098</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4097</v>
+        <v>0.4049</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4339</v>
+        <v>1.4172</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9504</v>
+        <v>-0.4421</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3108</v>
+        <v>-0.09180000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6395999999999999</v>
+        <v>-0.3503</v>
       </c>
       <c r="V9" t="n">
-        <v>0.9564</v>
+        <v>0.9779</v>
       </c>
       <c r="W9" t="n">
-        <v>0.7262</v>
+        <v>0.7528</v>
       </c>
       <c r="X9" t="n">
-        <v>0.2302</v>
+        <v>0.2251</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.1455</v>
+        <v>-1.2106</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8816000000000001</v>
+        <v>1.592</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.0271</v>
+        <v>-2.8026</v>
       </c>
       <c r="G10" t="n">
-        <v>3.5799</v>
+        <v>3.5859</v>
       </c>
       <c r="H10" t="n">
-        <v>1.1819</v>
+        <v>1.1858</v>
       </c>
       <c r="I10" t="n">
-        <v>2.398</v>
+        <v>2.4001</v>
       </c>
       <c r="J10" t="n">
-        <v>3.4002</v>
+        <v>3.4522</v>
       </c>
       <c r="K10" t="n">
-        <v>1.4889</v>
+        <v>1.5205</v>
       </c>
       <c r="L10" t="n">
-        <v>1.9112</v>
+        <v>1.9317</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1797</v>
+        <v>0.1337</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.307</v>
+        <v>-0.3346</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4868</v>
+        <v>0.4684</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.4097</v>
+        <v>-0.4049</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.0485</v>
+        <v>-2.0245</v>
       </c>
       <c r="R10" t="n">
-        <v>1.6388</v>
+        <v>1.6196</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.8978</v>
+        <v>-0.9529</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7121</v>
+        <v>-0.0866</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.1857</v>
+        <v>-0.8663</v>
       </c>
       <c r="V10" t="n">
-        <v>-3.4178</v>
+        <v>-3.4387</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2421</v>
+        <v>0.2509</v>
       </c>
       <c r="X10" t="n">
-        <v>-3.6599</v>
+        <v>-3.6896</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.8332</v>
+        <v>-3.4106</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.7734</v>
+        <v>-1.4667</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.0598</v>
+        <v>-1.9439</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.3001</v>
+        <v>-1.3062</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.1479</v>
+        <v>-0.1576</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.1522</v>
+        <v>-1.1485</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.295</v>
+        <v>-1.2849</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0195</v>
+        <v>0.0198</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.3145</v>
+        <v>-1.3047</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.0051</v>
+        <v>-0.0213</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1674</v>
+        <v>-0.1774</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1623</v>
+        <v>0.1561</v>
       </c>
       <c r="P11" t="n">
-        <v>0.4097</v>
+        <v>0.4049</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.4097</v>
+        <v>0.4049</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.16</v>
+        <v>-0.6982</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7205</v>
+        <v>-0.4327</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4395</v>
+        <v>-0.2655</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.7828</v>
+        <v>-1.8111</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2421</v>
+        <v>0.2509</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.0248</v>
+        <v>-2.062</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.9439</v>
+        <v>-3.6522</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.439</v>
+        <v>-2.3722</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.5049</v>
+        <v>-1.28</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.297</v>
+        <v>-1.3308</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.0533</v>
+        <v>-0.07779999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.2437</v>
+        <v>-1.253</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.4406</v>
+        <v>-0.4341</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0585</v>
+        <v>0.0593</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.4992</v>
+        <v>-0.4933</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.8564000000000001</v>
+        <v>-0.8968</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.1119</v>
+        <v>-0.1371</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.7445000000000001</v>
+        <v>-0.7597</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.4339</v>
+        <v>-1.4172</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.0485</v>
+        <v>-2.0245</v>
       </c>
       <c r="R12" t="n">
-        <v>0.6145</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7288</v>
+        <v>-0.4023</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0501</v>
+        <v>0.0864</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.779</v>
+        <v>-0.4887</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.4841</v>
+        <v>-0.5019</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.4841</v>
+        <v>-0.5019</v>
       </c>
     </row>
     <row r="13">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.314300000000002</v>
+        <v>4.560700000000002</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.8751999999999995</v>
+        <v>1.308099999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>4.1893</v>
+        <v>3.2525</v>
       </c>
       <c r="G13" t="n">
-        <v>13.5256</v>
+        <v>13.5122</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.8127</v>
+        <v>-1.8746</v>
       </c>
       <c r="I13" t="n">
-        <v>15.3383</v>
+        <v>15.3871</v>
       </c>
       <c r="J13" t="n">
-        <v>10.0318</v>
+        <v>10.4828</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.5536999999999997</v>
+        <v>-0.3087999999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>10.5851</v>
+        <v>10.7917</v>
       </c>
       <c r="M13" t="n">
-        <v>3.494100000000001</v>
+        <v>3.0294</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.2591</v>
+        <v>-1.5658</v>
       </c>
       <c r="O13" t="n">
-        <v>4.7534</v>
+        <v>4.5952</v>
       </c>
       <c r="P13" t="n">
-        <v>-3.0726</v>
+        <v>-3.036899999999999</v>
       </c>
       <c r="Q13" t="n">
-        <v>-16.3879</v>
+        <v>-16.1961</v>
       </c>
       <c r="R13" t="n">
-        <v>13.315</v>
+        <v>13.1595</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.8706</v>
+        <v>-1.5912</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4811999999999998</v>
+        <v>0.9415000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.3895</v>
+        <v>-2.5328</v>
       </c>
       <c r="V13" t="n">
-        <v>-4.2679</v>
+        <v>-4.3236</v>
       </c>
       <c r="W13" t="n">
-        <v>5.9626</v>
+        <v>6.079799999999999</v>
       </c>
       <c r="X13" t="n">
-        <v>-10.2304</v>
+        <v>-10.4034</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. ENABULELE OGUNSUYI</t>
+          <t>A. MEANA PEREZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.3906</v>
+        <v>3.0532</v>
       </c>
       <c r="E14" t="n">
-        <v>3.8491</v>
+        <v>1.4511</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4585</v>
+        <v>1.6021</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1924</v>
+        <v>-3.1123</v>
       </c>
       <c r="H14" t="n">
-        <v>1.7396</v>
+        <v>0.136</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.5472</v>
+        <v>-3.2483</v>
       </c>
       <c r="J14" t="n">
-        <v>2.551</v>
+        <v>-1.6912</v>
       </c>
       <c r="K14" t="n">
-        <v>2.3534</v>
+        <v>-0.083</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1976</v>
+        <v>-1.6082</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.3586</v>
+        <v>-1.4211</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.6138</v>
+        <v>0.219</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.7448</v>
+        <v>-1.6401</v>
       </c>
       <c r="P14" t="n">
-        <v>1.4339</v>
+        <v>-0.2025</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.0242</v>
+        <v>-3.0368</v>
       </c>
       <c r="R14" t="n">
-        <v>2.4582</v>
+        <v>2.8343</v>
       </c>
       <c r="S14" t="n">
-        <v>1.9767</v>
+        <v>0.6677999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>2.5347</v>
+        <v>0.2281</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5581</v>
+        <v>0.4398</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.2124</v>
+        <v>5.7001</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.2124</v>
+        <v>5.951</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-0.2509</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. MEANA PEREZ</t>
+          <t>M. ENABULELE OGUNSUYI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.1151</v>
+        <v>2.4356</v>
       </c>
       <c r="E15" t="n">
-        <v>0.7005</v>
+        <v>2.2892</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4146</v>
+        <v>0.1464</v>
       </c>
       <c r="G15" t="n">
-        <v>-3.1671</v>
+        <v>0.1786</v>
       </c>
       <c r="H15" t="n">
-        <v>0.08989999999999999</v>
+        <v>1.7583</v>
       </c>
       <c r="I15" t="n">
-        <v>-3.257</v>
+        <v>-1.5797</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.812</v>
+        <v>2.6076</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.1604</v>
+        <v>2.4088</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.6516</v>
+        <v>0.1988</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.3551</v>
+        <v>-2.429</v>
       </c>
       <c r="N15" t="n">
-        <v>0.2504</v>
+        <v>-0.6504</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.6054</v>
+        <v>-1.7785</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.2048</v>
+        <v>1.4172</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.0727</v>
+        <v>-1.0123</v>
       </c>
       <c r="R15" t="n">
-        <v>2.8679</v>
+        <v>2.4294</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1739</v>
+        <v>1.0264</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3178</v>
+        <v>0.8804</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1439</v>
+        <v>0.146</v>
       </c>
       <c r="V15" t="n">
-        <v>5.661</v>
+        <v>-0.1865</v>
       </c>
       <c r="W15" t="n">
-        <v>5.903</v>
+        <v>-0.1865</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.2421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P. BONO SOLER</t>
+          <t>J. PALAMOS MOLINS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9044</v>
+        <v>1.0484</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3823</v>
+        <v>0.9479</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.4779</v>
+        <v>0.1004</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.9008</v>
+        <v>0.615</v>
       </c>
       <c r="H16" t="n">
-        <v>1.5304</v>
+        <v>0.4545</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.4312</v>
+        <v>0.1605</v>
       </c>
       <c r="J16" t="n">
-        <v>1.1639</v>
+        <v>1.1521</v>
       </c>
       <c r="K16" t="n">
-        <v>1.7817</v>
+        <v>0.6117</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.6177</v>
+        <v>0.5403</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.0647</v>
+        <v>-0.5371</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.2512</v>
+        <v>-0.1572</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.8135</v>
+        <v>-0.3798</v>
       </c>
       <c r="P16" t="n">
-        <v>1.2291</v>
+        <v>0.4049</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.2291</v>
+        <v>0.4049</v>
       </c>
       <c r="S16" t="n">
-        <v>0.334</v>
+        <v>0.2794</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0237</v>
+        <v>0.1401</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3578</v>
+        <v>0.1394</v>
       </c>
       <c r="V16" t="n">
-        <v>0.2421</v>
+        <v>-0.2509</v>
       </c>
       <c r="W16" t="n">
-        <v>0.2421</v>
+        <v>-0.3442</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>0.09320000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8144</v>
+        <v>1.025</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8356</v>
+        <v>1.9614</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.0212</v>
+        <v>-0.9364</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.1449</v>
+        <v>-2.161</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.6413</v>
+        <v>-0.6518</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.5037</v>
+        <v>-1.5092</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.0734</v>
+        <v>-1.0193</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.9194</v>
+        <v>-0.891</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.154</v>
+        <v>-0.1283</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.0715</v>
+        <v>-1.1418</v>
       </c>
       <c r="N17" t="n">
-        <v>0.2781</v>
+        <v>0.2392</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.3496</v>
+        <v>-1.381</v>
       </c>
       <c r="P17" t="n">
-        <v>1.6388</v>
+        <v>1.6196</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R17" t="n">
-        <v>2.663</v>
+        <v>2.6319</v>
       </c>
       <c r="S17" t="n">
-        <v>1.0784</v>
+        <v>1.3154</v>
       </c>
       <c r="T17" t="n">
-        <v>0.8458</v>
+        <v>0.8597</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2326</v>
+        <v>0.4558</v>
       </c>
       <c r="V17" t="n">
-        <v>0.2421</v>
+        <v>0.2509</v>
       </c>
       <c r="W17" t="n">
-        <v>3.0874</v>
+        <v>3.1332</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.8453</v>
+        <v>-2.8823</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. PALAMOS MOLINS</t>
+          <t>K. CLEMENT AIGBOGUN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5656</v>
+        <v>0.7785</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5914</v>
+        <v>-0.0113</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0258</v>
+        <v>0.7899</v>
       </c>
       <c r="G18" t="n">
-        <v>0.6076</v>
+        <v>0.872</v>
       </c>
       <c r="H18" t="n">
-        <v>0.4516</v>
+        <v>0.1785</v>
       </c>
       <c r="I18" t="n">
-        <v>0.156</v>
+        <v>0.6935</v>
       </c>
       <c r="J18" t="n">
-        <v>1.1195</v>
+        <v>1.2554</v>
       </c>
       <c r="K18" t="n">
-        <v>0.5911999999999999</v>
+        <v>0.079</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5282</v>
+        <v>1.1764</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.5119</v>
+        <v>-0.3834</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1396</v>
+        <v>0.0994</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.3722</v>
+        <v>-0.4829</v>
       </c>
       <c r="P18" t="n">
-        <v>0.4097</v>
+        <v>0.2025</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.0123</v>
       </c>
       <c r="R18" t="n">
-        <v>0.4097</v>
+        <v>1.2147</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2096</v>
+        <v>-0.2959</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1798</v>
+        <v>-0.2545</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0298</v>
+        <v>-0.0414</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.2421</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.3482</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0.1062</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>K. CLEMENT AIGBOGUN</t>
+          <t>P. BONO SOLER</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0992</v>
+        <v>0.6877</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.3669</v>
+        <v>1.3391</v>
       </c>
       <c r="F19" t="n">
-        <v>0.466</v>
+        <v>-0.6514</v>
       </c>
       <c r="G19" t="n">
-        <v>0.884</v>
+        <v>-0.9029</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1894</v>
+        <v>1.5413</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6947</v>
+        <v>-2.4442</v>
       </c>
       <c r="J19" t="n">
-        <v>1.2385</v>
+        <v>1.2042</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0781</v>
+        <v>1.8168</v>
       </c>
       <c r="L19" t="n">
-        <v>1.1605</v>
+        <v>-0.6126</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.3545</v>
+        <v>-2.1071</v>
       </c>
       <c r="N19" t="n">
-        <v>0.1113</v>
+        <v>-0.2755</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.4658</v>
+        <v>-1.8316</v>
       </c>
       <c r="P19" t="n">
-        <v>0.2048</v>
+        <v>1.2147</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.0242</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.2291</v>
+        <v>1.2147</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.9897</v>
+        <v>0.125</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5810999999999999</v>
+        <v>-0.1161</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4086</v>
+        <v>0.2411</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.2509</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.2509</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S. GALLEGO MOGRO</t>
+          <t>A. RIVAS PALMER</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.7032</v>
+        <v>-0.3635</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.262</v>
+        <v>-3.4951</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4413</v>
+        <v>3.1316</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.3674</v>
+        <v>-1.351</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.1116</v>
+        <v>0.7311</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2558</v>
+        <v>-2.0821</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>-1.9981</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>-0.0013</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>-1.9968</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.3674</v>
+        <v>0.6471</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1116</v>
+        <v>0.7324000000000001</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2558</v>
+        <v>-0.0853</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>-0.4049</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-2.0245</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.6196</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3358</v>
+        <v>1.6434</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.262</v>
+        <v>0.5275</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.07389999999999999</v>
+        <v>1.1159</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.2509</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.2509</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. KANDULU</t>
+          <t>D. RIVAS PALMER</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.9003</v>
+        <v>-0.3845</v>
       </c>
       <c r="E21" t="n">
-        <v>1.2027</v>
+        <v>-1.3922</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.103</v>
+        <v>1.0077</v>
       </c>
       <c r="G21" t="n">
-        <v>1.1887</v>
+        <v>-0.7331</v>
       </c>
       <c r="H21" t="n">
-        <v>1.5609</v>
+        <v>-0.0985</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3722</v>
+        <v>-0.6346000000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>0.9758</v>
+        <v>-1.3247</v>
       </c>
       <c r="K21" t="n">
-        <v>0.9758</v>
+        <v>-0.6723</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>-0.6523</v>
       </c>
       <c r="M21" t="n">
-        <v>0.2129</v>
+        <v>0.5915</v>
       </c>
       <c r="N21" t="n">
-        <v>0.5852000000000001</v>
+        <v>0.5738</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.3722</v>
+        <v>0.0177</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.2048</v>
+        <v>0.2025</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.0242</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.8194</v>
+        <v>0.2025</v>
       </c>
       <c r="S21" t="n">
-        <v>1.7639</v>
+        <v>0.1462</v>
       </c>
       <c r="T21" t="n">
-        <v>1.7056</v>
+        <v>-0.06759999999999999</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0583</v>
+        <v>0.2138</v>
       </c>
       <c r="V21" t="n">
-        <v>-3.648</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.4544</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-3.1936</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D. RIVAS PALMER</t>
+          <t>S. GALLEGO MOGRO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,58 +2125,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.9360000000000001</v>
+        <v>-0.7079</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.5143</v>
+        <v>-0.2561</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5782</v>
+        <v>-0.4518</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.7264</v>
+        <v>-0.3774</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.0921</v>
+        <v>-0.1183</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.6343</v>
+        <v>-0.2591</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.3345</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.6772</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6572</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.6081</v>
+        <v>-0.3774</v>
       </c>
       <c r="N22" t="n">
-        <v>0.5852000000000001</v>
+        <v>-0.1183</v>
       </c>
       <c r="O22" t="n">
-        <v>0.0229</v>
+        <v>-0.2591</v>
       </c>
       <c r="P22" t="n">
-        <v>0.2048</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.2048</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4144</v>
+        <v>-0.3305</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1798</v>
+        <v>-0.2561</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2347</v>
+        <v>-0.07439999999999999</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. RIVAS PALMER</t>
+          <t>D. KANDULU</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.1246</v>
+        <v>-1.8566</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.5122</v>
+        <v>0.09859999999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>3.3876</v>
+        <v>-1.9552</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.3571</v>
+        <v>1.1817</v>
       </c>
       <c r="H23" t="n">
-        <v>0.7248</v>
+        <v>1.5616</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.0819</v>
+        <v>-0.3798</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.0387</v>
+        <v>0.9877</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.0275</v>
+        <v>0.9877</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.0112</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.6816</v>
+        <v>0.194</v>
       </c>
       <c r="N23" t="n">
-        <v>0.7523</v>
+        <v>0.5738</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.0706</v>
+        <v>-0.3798</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.4097</v>
+        <v>-0.2025</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.0485</v>
+        <v>-1.0123</v>
       </c>
       <c r="R23" t="n">
-        <v>1.6388</v>
+        <v>0.8098</v>
       </c>
       <c r="S23" t="n">
-        <v>0.8842</v>
+        <v>0.8279</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4251</v>
+        <v>0.5605</v>
       </c>
       <c r="U23" t="n">
-        <v>1.3093</v>
+        <v>0.2674</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.2421</v>
+        <v>-3.6638</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>-0.4374</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.2421</v>
+        <v>-3.2264</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.7048</v>
+        <v>-2.2316</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.84</v>
+        <v>-1.4777</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.8648</v>
+        <v>-0.7539</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.6915</v>
+        <v>-3.6881</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.5161</v>
+        <v>-1.503</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.1754</v>
+        <v>-2.1851</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.7713</v>
+        <v>-1.7406</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.1535</v>
+        <v>-1.128</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.6177</v>
+        <v>-0.6126</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.9203</v>
+        <v>-1.9474</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.3625</v>
+        <v>-0.3749</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.5577</v>
+        <v>-1.5725</v>
       </c>
       <c r="P24" t="n">
-        <v>1.2291</v>
+        <v>1.2147</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.2291</v>
+        <v>1.2147</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2423</v>
+        <v>0.2418</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3108</v>
+        <v>0.012</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0684</v>
+        <v>0.2298</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>0.2421</v>
+        <v>0.2509</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.2421</v>
+        <v>-0.2509</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.8346</v>
+        <v>-3.9961</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.2555</v>
+        <v>-4.7074</v>
       </c>
       <c r="F25" t="n">
-        <v>0.4209</v>
+        <v>0.7114</v>
       </c>
       <c r="G25" t="n">
-        <v>-4.0429</v>
+        <v>-4.0337</v>
       </c>
       <c r="H25" t="n">
-        <v>-2.1128</v>
+        <v>-2.115</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.9301</v>
+        <v>-1.9187</v>
       </c>
       <c r="J25" t="n">
-        <v>-2.5127</v>
+        <v>-2.4625</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.5829</v>
+        <v>-1.5626</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.9298</v>
+        <v>-0.8999</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.5302</v>
+        <v>-1.5712</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.5299</v>
+        <v>-0.5523</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.0003</v>
+        <v>-1.0188</v>
       </c>
       <c r="P25" t="n">
-        <v>-2.4582</v>
+        <v>-2.4294</v>
       </c>
       <c r="Q25" t="n">
-        <v>-4.097</v>
+        <v>-4.049</v>
       </c>
       <c r="R25" t="n">
-        <v>1.6388</v>
+        <v>1.6196</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.8008999999999999</v>
+        <v>-0.0066</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.4167</v>
+        <v>0.0188</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.3842</v>
+        <v>-0.0254</v>
       </c>
       <c r="V25" t="n">
-        <v>2.4674</v>
+        <v>2.4736</v>
       </c>
       <c r="W25" t="n">
-        <v>1.7709</v>
+        <v>1.7853</v>
       </c>
       <c r="X25" t="n">
-        <v>0.6965</v>
+        <v>0.6883</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-3.3142</v>
+        <v>-0.5118000000000023</v>
       </c>
       <c r="E26" t="n">
-        <v>-4.189299999999999</v>
+        <v>-3.2525</v>
       </c>
       <c r="F26" t="n">
-        <v>0.8747999999999998</v>
+        <v>2.740800000000002</v>
       </c>
       <c r="G26" t="n">
-        <v>-13.5254</v>
+        <v>-13.5122</v>
       </c>
       <c r="H26" t="n">
-        <v>1.8127</v>
+        <v>1.874699999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>-15.3381</v>
+        <v>-15.3868</v>
       </c>
       <c r="J26" t="n">
-        <v>-3.493900000000001</v>
+        <v>-3.0294</v>
       </c>
       <c r="K26" t="n">
-        <v>1.2593</v>
+        <v>1.565799999999999</v>
       </c>
       <c r="L26" t="n">
-        <v>-4.7529</v>
+        <v>-4.5952</v>
       </c>
       <c r="M26" t="n">
-        <v>-10.0316</v>
+        <v>-10.4829</v>
       </c>
       <c r="N26" t="n">
-        <v>0.5539000000000001</v>
+        <v>0.3090000000000002</v>
       </c>
       <c r="O26" t="n">
-        <v>-10.585</v>
+        <v>-10.7917</v>
       </c>
       <c r="P26" t="n">
-        <v>3.072699999999999</v>
+        <v>3.0368</v>
       </c>
       <c r="Q26" t="n">
-        <v>-13.315</v>
+        <v>-13.1595</v>
       </c>
       <c r="R26" t="n">
-        <v>16.3879</v>
+        <v>16.1961</v>
       </c>
       <c r="S26" t="n">
-        <v>2.8706</v>
+        <v>5.6403</v>
       </c>
       <c r="T26" t="n">
-        <v>2.3893</v>
+        <v>2.5328</v>
       </c>
       <c r="U26" t="n">
-        <v>0.481</v>
+        <v>3.1078</v>
       </c>
       <c r="V26" t="n">
-        <v>4.268</v>
+        <v>4.323399999999999</v>
       </c>
       <c r="W26" t="n">
-        <v>10.2305</v>
+        <v>10.4032</v>
       </c>
       <c r="X26" t="n">
-        <v>-5.962499999999999</v>
+        <v>-6.0799</v>
       </c>
     </row>
   </sheetData>
